--- a/petme2-ads-agent/outbox/2026-10-05/bulk-upload-3-test-campaigns.xlsx
+++ b/petme2-ads-agent/outbox/2026-10-05/bulk-upload-3-test-campaigns.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y161"/>
+  <dimension ref="A1:Y241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -873,23 +873,20 @@
           <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Test-DualFeeders</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Test - Dual Feeders</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="R10" t="n">
-        <v>0.4</v>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -900,7 +897,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -913,19 +910,19 @@
           <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Test-DualFeeders</t>
-        </is>
-      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>LW-EZAJ-KKZD</t>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>wireless</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -937,7 +934,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -950,19 +947,19 @@
           <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Test-DualFeeders</t>
-        </is>
-      </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>93-E8EG-20UY</t>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>ceramic</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -974,7 +971,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -987,27 +984,19 @@
           <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Test-DualFeeders</t>
-        </is>
-      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="S13" t="n">
-        <v>0.55</v>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>dual cat feeder</t>
+          <t>outdoor</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1008,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1032,27 +1021,19 @@
           <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Test-DualFeeders</t>
-        </is>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="S14" t="n">
-        <v>0.55</v>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>dual pet feeder</t>
+          <t>heated</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1045,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1077,27 +1058,19 @@
           <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Test-DualFeeders</t>
-        </is>
-      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="S15" t="n">
-        <v>0.55</v>
-      </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>auto cat feeder</t>
+          <t>large dog</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1082,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1122,27 +1095,19 @@
           <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Test-DualFeeders</t>
-        </is>
-      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="S16" t="n">
-        <v>0.55</v>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>cat food dispenser</t>
+          <t>wet food</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1119,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1172,23 +1137,18 @@
           <t>Test-DualFeeders</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Test - Dual Feeders</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="S17" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>automatic dog feeder</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
+      <c r="R17" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="18">
@@ -1199,7 +1159,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1222,17 +1182,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S18" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>timed pet feeder</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>phrase</t>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>LW-EZAJ-KKZD</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1196,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1267,17 +1219,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S19" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>cat feeder for 2 cats</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>phrase</t>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>93-E8EG-20UY</t>
         </is>
       </c>
     </row>
@@ -1313,11 +1257,11 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>automatic cat feeder 2 cats</t>
+          <t>dual cat feeder</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -1358,11 +1302,11 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>automatic cat feeder for two cats</t>
+          <t>dual pet feeder</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -1403,11 +1347,11 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>automatic feeder for 2 cats</t>
+          <t>auto cat feeder</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -1452,7 +1396,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>dual automatic cat feeder</t>
+          <t>cat food dispenser</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -1497,7 +1441,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>dual bowl automatic cat feeder</t>
+          <t>automatic dog feeder</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -1538,11 +1482,11 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>automatic cat feeder with 2 bowls</t>
+          <t>timed pet feeder</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -1587,7 +1531,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>automatic cat feeder with stainless steel bowls</t>
+          <t>cat feeder for 2 cats</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -1628,11 +1572,11 @@
         </is>
       </c>
       <c r="S27" t="n">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>cat food dispenser for 2 cats</t>
+          <t>automatic cat feeder 2 cats</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -1677,7 +1621,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>automatic pet feeder for 2 cats</t>
+          <t>automatic cat feeder for two cats</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -1722,7 +1666,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>automatic cat food dispenser</t>
+          <t>automatic feeder for 2 cats</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -1767,7 +1711,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>automatic cat feeder dry food</t>
+          <t>dual automatic cat feeder</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -1812,7 +1756,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>cat feeder with timer</t>
+          <t>dual bowl automatic cat feeder</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -1857,7 +1801,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>automatic cat feeder 2 way audio</t>
+          <t>automatic cat feeder with 2 bowls</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -1902,7 +1846,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>quiet automatic cat feeder</t>
+          <t>automatic cat feeder with stainless steel bowls</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -1947,7 +1891,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>automatic dog feeder for small dogs</t>
+          <t>automatic pet feeder for 2 cats</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -1992,7 +1936,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>pet food dispenser automatic</t>
+          <t>automatic cat feeder dry food</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -2037,7 +1981,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>3l automatic cat feeder</t>
+          <t>cat feeder with timer</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -2054,7 +1998,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2069,12 +2013,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Test - WiFi Feeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2082,8 +2021,18 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="R37" t="n">
-        <v>0.2</v>
+      <c r="S37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>automatic cat feeder 2 way audio</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -2094,7 +2043,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2109,7 +2058,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2117,9 +2066,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>QO-7VBS-CVT4</t>
+      <c r="S38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>quiet automatic cat feeder</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2103,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -2155,11 +2112,11 @@
         </is>
       </c>
       <c r="S39" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>wifi pet feeder</t>
+          <t>automatic dog feeder for small dogs</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -2191,7 +2148,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -2200,11 +2157,11 @@
         </is>
       </c>
       <c r="S40" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>smart pet feeder</t>
+          <t>pet food dispenser automatic</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -2236,7 +2193,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -2245,11 +2202,11 @@
         </is>
       </c>
       <c r="S41" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>smart cat feeder</t>
+          <t>3l automatic cat feeder</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -2281,7 +2238,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -2290,11 +2247,11 @@
         </is>
       </c>
       <c r="S42" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>wifi dog feeder</t>
+          <t>cat feeder automatic</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -2326,7 +2283,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -2335,11 +2292,11 @@
         </is>
       </c>
       <c r="S43" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>smart dog feeder</t>
+          <t>cat automatic feeders</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -2371,7 +2328,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -2380,11 +2337,11 @@
         </is>
       </c>
       <c r="S44" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>wifi automatic cat feeder</t>
+          <t>dog feeder automatic</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -2416,7 +2373,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -2425,11 +2382,11 @@
         </is>
       </c>
       <c r="S45" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>automatic cat feeder wifi</t>
+          <t>dog automatic feeders</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -2461,7 +2418,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -2470,11 +2427,11 @@
         </is>
       </c>
       <c r="S46" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>smart automatic cat feeder</t>
+          <t>auto dog feeder</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -2506,7 +2463,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -2515,11 +2472,11 @@
         </is>
       </c>
       <c r="S47" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>wifi cat feeder for 2 cats</t>
+          <t>automatic feeder cat dry food</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -2551,7 +2508,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -2560,11 +2517,11 @@
         </is>
       </c>
       <c r="S48" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>wifi automatic dog feeder</t>
+          <t>auto feeder cat food</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -2596,7 +2553,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -2605,11 +2562,11 @@
         </is>
       </c>
       <c r="S49" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>automatic pet feeder wifi</t>
+          <t>cat auto feeder</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -2641,7 +2598,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -2650,11 +2607,11 @@
         </is>
       </c>
       <c r="S50" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>automatic cat feeder with app control</t>
+          <t>dog food dispenser automatic</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -2686,7 +2643,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -2695,11 +2652,11 @@
         </is>
       </c>
       <c r="S51" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>cat feeder app control</t>
+          <t>pet feeder automatic</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -2731,7 +2688,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -2740,11 +2697,11 @@
         </is>
       </c>
       <c r="S52" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>pet feeder with app</t>
+          <t>automatic dog food dispenser</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -2776,7 +2733,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -2785,11 +2742,11 @@
         </is>
       </c>
       <c r="S53" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>cat feeder with voice recorder</t>
+          <t>automatic food dispenser for cats</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -2821,7 +2778,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -2830,11 +2787,11 @@
         </is>
       </c>
       <c r="S54" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>automatic cat feeder with voice recording</t>
+          <t>timed cat feeders for dry food</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -2866,7 +2823,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -2875,11 +2832,11 @@
         </is>
       </c>
       <c r="S55" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>5l automatic cat feeder</t>
+          <t>cat food automatic feeder</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -2911,7 +2868,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -2920,11 +2877,11 @@
         </is>
       </c>
       <c r="S56" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>automatic cat feeder 5l</t>
+          <t>timed dog feeder</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -2956,7 +2913,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -2965,11 +2922,11 @@
         </is>
       </c>
       <c r="S57" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>large capacity automatic cat feeder</t>
+          <t>double cat feeder</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -3001,7 +2958,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -3010,11 +2967,11 @@
         </is>
       </c>
       <c r="S58" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>elevated automatic cat feeder</t>
+          <t>auto pet feeder</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -3046,7 +3003,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -3055,11 +3012,11 @@
         </is>
       </c>
       <c r="S59" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>wifi cat food dispenser</t>
+          <t>auto feeder dog food</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -3091,7 +3048,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -3100,11 +3057,11 @@
         </is>
       </c>
       <c r="S60" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>smart cat food dispenser</t>
+          <t>automatic cat feeder programmable</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -3136,7 +3093,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -3145,11 +3102,11 @@
         </is>
       </c>
       <c r="S61" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>automatic dog feeder wifi</t>
+          <t>automatic feeder dog dry food</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -3181,7 +3138,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -3190,11 +3147,11 @@
         </is>
       </c>
       <c r="S62" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>wifi automatic pet feeder for 2 cats</t>
+          <t>double automatic cat feeder</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -3226,7 +3183,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Test-WiFiFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -3235,11 +3192,11 @@
         </is>
       </c>
       <c r="S63" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>smart dual bowl cat feeder</t>
+          <t>dog food automatic feeder</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -3256,7 +3213,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3271,12 +3228,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Test - Camera Feeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -3284,8 +3236,18 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="R64" t="n">
-        <v>0.4</v>
+      <c r="S64" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>automatic food dispenser for dogs</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -3296,7 +3258,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3311,7 +3273,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -3319,9 +3281,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>2H-2T1T-CJC3</t>
+      <c r="S65" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>timed feeder for cats</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3318,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -3357,11 +3327,11 @@
         </is>
       </c>
       <c r="S66" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>camera cat feeder</t>
+          <t>automatic pet feeder for dogs</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -3393,7 +3363,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -3402,11 +3372,11 @@
         </is>
       </c>
       <c r="S67" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>camera pet feeder</t>
+          <t>2 cat automatic feeder</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -3438,7 +3408,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -3447,11 +3417,11 @@
         </is>
       </c>
       <c r="S68" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>camera dog feeder</t>
+          <t>two cat automatic feeder</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -3483,7 +3453,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -3492,11 +3462,11 @@
         </is>
       </c>
       <c r="S69" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>pet camera feeder</t>
+          <t>timed dog food dispenser</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -3528,7 +3498,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-DualFeeders</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -3537,11 +3507,11 @@
         </is>
       </c>
       <c r="S70" t="n">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>dog feeder with camera</t>
+          <t>autofeeder cat food</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -3558,7 +3528,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3573,7 +3543,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Test - WiFi Feeder</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -3581,18 +3556,8 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S71" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>automatic pet feeder with camera</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
+      <c r="R71" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="72">
@@ -3603,7 +3568,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3618,7 +3583,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -3626,17 +3591,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S72" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>cat food dispenser with camera</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>phrase</t>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>QO-7VBS-CVT4</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3620,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -3672,11 +3629,11 @@
         </is>
       </c>
       <c r="S73" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>dog food dispenser with camera</t>
+          <t>wifi automatic cat feeder</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -3708,7 +3665,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -3717,11 +3674,11 @@
         </is>
       </c>
       <c r="S74" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>wifi cat feeder with camera</t>
+          <t>smart automatic cat feeder</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -3753,7 +3710,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -3762,11 +3719,11 @@
         </is>
       </c>
       <c r="S75" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>smart pet feeder with camera</t>
+          <t>wifi cat feeder for 2 cats</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -3798,7 +3755,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -3807,11 +3764,11 @@
         </is>
       </c>
       <c r="S76" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>smart cat feeder with camera</t>
+          <t>wifi automatic dog feeder</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -3843,7 +3800,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -3852,11 +3809,11 @@
         </is>
       </c>
       <c r="S77" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>automatic feeder with camera</t>
+          <t>automatic pet feeder wifi</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -3888,7 +3845,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -3897,11 +3854,11 @@
         </is>
       </c>
       <c r="S78" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>auto cat feeder with camera</t>
+          <t>cat feeder app control</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -3933,7 +3890,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -3942,11 +3899,11 @@
         </is>
       </c>
       <c r="S79" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>automatic cat feeder with camera and audio</t>
+          <t>pet feeder with app</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -3978,7 +3935,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -3987,11 +3944,11 @@
         </is>
       </c>
       <c r="S80" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>cat feeder with camera 2 way audio</t>
+          <t>cat feeder with voice recorder</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -4023,7 +3980,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -4032,11 +3989,11 @@
         </is>
       </c>
       <c r="S81" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>pet feeder camera 2 way audio</t>
+          <t>automatic cat feeder with voice recording</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -4068,7 +4025,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -4077,11 +4034,11 @@
         </is>
       </c>
       <c r="S82" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>pet feeder with camera and app</t>
+          <t>5l automatic cat feeder</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -4113,7 +4070,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -4122,11 +4079,11 @@
         </is>
       </c>
       <c r="S83" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>automatic cat feeder 1080p camera</t>
+          <t>automatic cat feeder 5l</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -4158,7 +4115,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -4167,11 +4124,11 @@
         </is>
       </c>
       <c r="S84" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>cat feeder with hd camera</t>
+          <t>large capacity automatic cat feeder</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -4203,7 +4160,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -4212,11 +4169,11 @@
         </is>
       </c>
       <c r="S85" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>automatic cat feeder with video</t>
+          <t>elevated automatic cat feeder</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -4248,7 +4205,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -4257,11 +4214,11 @@
         </is>
       </c>
       <c r="S86" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>camera feeder for cats</t>
+          <t>automatic dog feeder wifi</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -4293,7 +4250,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -4302,11 +4259,11 @@
         </is>
       </c>
       <c r="S87" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>automatic cat feeder with camera wifi</t>
+          <t>wifi automatic pet feeder for 2 cats</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -4338,7 +4295,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Test-CameraFeeder</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -4347,11 +4304,11 @@
         </is>
       </c>
       <c r="S88" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>cat feeder with camera for small dogs</t>
+          <t>smart dual bowl cat feeder</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -4368,7 +4325,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4383,12 +4340,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Test - Stainless Fountain</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -4396,8 +4348,18 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="R89" t="n">
-        <v>0.4</v>
+      <c r="S89" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>large capacity automatic dog feeder</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -4408,7 +4370,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4423,7 +4385,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -4431,9 +4393,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>QY-HHE8-0H1B</t>
+      <c r="S90" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>cat feeder with app</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4430,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -4469,11 +4439,11 @@
         </is>
       </c>
       <c r="S91" t="n">
-        <v>0.55</v>
+        <v>0.2</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>dog water fountain</t>
+          <t>elevated automatic dog feeder</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -4490,7 +4460,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4505,7 +4475,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Test - Camera Feeder</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -4513,18 +4488,8 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S92" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>metal pet fountain</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
+      <c r="R92" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="93">
@@ -4535,7 +4500,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4550,7 +4515,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -4558,17 +4523,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S93" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>metal dog fountain</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>phrase</t>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>2H-2T1T-CJC3</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4552,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -4604,11 +4561,11 @@
         </is>
       </c>
       <c r="S94" t="n">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>steel cat fountain</t>
+          <t>camera cat feeder</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -4640,7 +4597,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -4653,7 +4610,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>dog fountain</t>
+          <t>camera pet feeder</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -4685,7 +4642,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -4694,11 +4651,11 @@
         </is>
       </c>
       <c r="S96" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>stainless steel dog water fountain</t>
+          <t>camera dog feeder</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -4730,7 +4687,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -4739,11 +4696,11 @@
         </is>
       </c>
       <c r="S97" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>stainless steel pet water fountain</t>
+          <t>pet camera feeder</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -4775,7 +4732,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -4784,11 +4741,11 @@
         </is>
       </c>
       <c r="S98" t="n">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>stainless steel pet fountain</t>
+          <t>dog feeder with camera</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -4820,7 +4777,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -4833,7 +4790,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>stainless steel cat fountain</t>
+          <t>automatic pet feeder with camera</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -4865,7 +4822,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -4874,11 +4831,11 @@
         </is>
       </c>
       <c r="S100" t="n">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>dog water fountain stainless steel</t>
+          <t>cat food dispenser with camera</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -4910,7 +4867,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -4923,7 +4880,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>pet water fountain stainless steel</t>
+          <t>dog food dispenser with camera</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -4955,7 +4912,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -4968,7 +4925,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>stainless steel water fountain for cats</t>
+          <t>wifi cat feeder with camera</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -5000,7 +4957,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -5013,7 +4970,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>stainless steel water fountain for dogs</t>
+          <t>smart pet feeder with camera</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -5045,7 +5002,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -5058,7 +5015,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>metal dog water fountain</t>
+          <t>smart cat feeder with camera</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -5090,7 +5047,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -5099,11 +5056,11 @@
         </is>
       </c>
       <c r="S105" t="n">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>metal pet water fountain</t>
+          <t>automatic feeder with camera</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -5135,7 +5092,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -5148,7 +5105,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>108oz cat water fountain</t>
+          <t>auto cat feeder with camera</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -5180,7 +5137,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -5193,7 +5150,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>3.2l cat water fountain</t>
+          <t>automatic cat feeder with camera and audio</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -5225,7 +5182,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -5238,7 +5195,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>108 oz pet water fountain</t>
+          <t>cat feeder with camera 2 way audio</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -5270,7 +5227,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -5283,7 +5240,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>large cat water fountain stainless steel</t>
+          <t>pet feeder camera 2 way audio</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -5315,7 +5272,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -5328,7 +5285,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>cat water fountain with led light</t>
+          <t>pet feeder with camera and app</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -5360,7 +5317,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -5373,7 +5330,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>pet water fountain with led light</t>
+          <t>automatic cat feeder 1080p camera</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -5405,7 +5362,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -5418,7 +5375,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>faucet cat water fountain</t>
+          <t>cat feeder with hd camera</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -5450,7 +5407,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -5463,7 +5420,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>cat water fountain dishwasher safe</t>
+          <t>automatic cat feeder with video</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -5495,7 +5452,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -5508,7 +5465,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>cat water fountain for multiple cats</t>
+          <t>camera feeder for cats</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -5540,7 +5497,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -5553,7 +5510,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>quiet stainless steel cat water fountain</t>
+          <t>automatic cat feeder with camera wifi</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -5585,7 +5542,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -5598,7 +5555,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>large capacity cat water fountain</t>
+          <t>cat feeder with camera for small dogs</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -5630,7 +5587,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Test-StainlessFountain</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -5639,11 +5596,11 @@
         </is>
       </c>
       <c r="S117" t="n">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>dog water fountain for small dogs</t>
+          <t>wifi automatic cat feeder app control</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -5660,7 +5617,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5675,12 +5632,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>Test - Basic Fountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -5688,8 +5640,18 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="R118" t="n">
-        <v>0.2</v>
+      <c r="S118" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>smart cat feeder</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -5700,7 +5662,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5715,7 +5677,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -5723,9 +5685,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>L6-L3S1-I7Q6</t>
+      <c r="S119" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>smart pet feeder</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5707,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5752,7 +5722,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -5760,9 +5730,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>SD-85ET-IOZ3</t>
+      <c r="S120" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>smart automatic dog feeder wifi app control</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5752,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5789,7 +5767,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -5797,9 +5775,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>JE-LQEW-9EHL</t>
+      <c r="S121" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>automatic cat feeder wifi</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5812,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -5835,11 +5821,11 @@
         </is>
       </c>
       <c r="S122" t="n">
-        <v>0.24</v>
+        <v>0.74</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>cat fountain</t>
+          <t>smart feeder for cats</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -5871,7 +5857,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -5880,11 +5866,11 @@
         </is>
       </c>
       <c r="S123" t="n">
-        <v>0.24</v>
+        <v>0.74</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>pet fountain</t>
+          <t>smart dog feeder</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
@@ -5916,7 +5902,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -5925,11 +5911,11 @@
         </is>
       </c>
       <c r="S124" t="n">
-        <v>0.24</v>
+        <v>0.74</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>cat water dispenser</t>
+          <t>wifi dog feeder</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -5961,7 +5947,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -5970,11 +5956,11 @@
         </is>
       </c>
       <c r="S125" t="n">
-        <v>0.24</v>
+        <v>0.74</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>cat drinking fountain</t>
+          <t>automatic cat feeder with camera 1080p</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -6006,7 +5992,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -6015,11 +6001,11 @@
         </is>
       </c>
       <c r="S126" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>pet water dispenser</t>
+          <t>wifi cat feeder app control</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -6051,7 +6037,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -6060,11 +6046,11 @@
         </is>
       </c>
       <c r="S127" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>kitty water fountain</t>
+          <t>automatic cat feeder battery backup</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -6096,7 +6082,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -6105,11 +6091,11 @@
         </is>
       </c>
       <c r="S128" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>pet drinking fountain</t>
+          <t>wi-fi enabled automatic cat feeder with app control</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -6141,7 +6127,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -6150,11 +6136,11 @@
         </is>
       </c>
       <c r="S129" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>quiet cat water fountain</t>
+          <t>automatic dog feeder with wifi</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
@@ -6186,7 +6172,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -6195,11 +6181,11 @@
         </is>
       </c>
       <c r="S130" t="n">
-        <v>0.2</v>
+        <v>0.74</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>cat water fountain quiet</t>
+          <t>wifi pet feeder</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -6231,7 +6217,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -6240,11 +6226,11 @@
         </is>
       </c>
       <c r="S131" t="n">
-        <v>0.2</v>
+        <v>0.74</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>silent cat water fountain</t>
+          <t>smart feeder with camera</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -6276,7 +6262,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -6285,11 +6271,11 @@
         </is>
       </c>
       <c r="S132" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>pet water fountain for cats</t>
+          <t>smart cat food dispensers</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -6321,7 +6307,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -6330,11 +6316,11 @@
         </is>
       </c>
       <c r="S133" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>automatic water dispenser for cats</t>
+          <t>smart cam feeder</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
@@ -6366,7 +6352,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -6375,11 +6361,11 @@
         </is>
       </c>
       <c r="S134" t="n">
-        <v>0.2</v>
+        <v>0.74</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>cat water fountain for indoor cats</t>
+          <t>wifi enabled automatic cat feeder</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -6411,7 +6397,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -6420,11 +6406,11 @@
         </is>
       </c>
       <c r="S135" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>water fountain for cats indoor</t>
+          <t>smart petfeeder</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
@@ -6456,7 +6442,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -6465,11 +6451,11 @@
         </is>
       </c>
       <c r="S136" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>plastic cat water fountain</t>
+          <t>wifi cat food dispenser</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -6501,7 +6487,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -6510,11 +6496,11 @@
         </is>
       </c>
       <c r="S137" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>cat water fountain with water level window</t>
+          <t>smart dog food dispenser</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
@@ -6531,7 +6517,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6546,7 +6532,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Test - Stainless Fountain</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -6554,18 +6545,8 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S138" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>pet water fountain for small dogs</t>
-        </is>
-      </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
+      <c r="R138" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="139">
@@ -6576,7 +6557,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6591,7 +6572,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -6599,17 +6580,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S139" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>kitten water fountain</t>
-        </is>
-      </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>phrase</t>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>QY-HHE8-0H1B</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6609,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -6645,11 +6618,11 @@
         </is>
       </c>
       <c r="S140" t="n">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>water bowl fountain for cats</t>
+          <t>metal pet fountain</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -6681,7 +6654,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Test-BasicFountains</t>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -6690,11 +6663,11 @@
         </is>
       </c>
       <c r="S141" t="n">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>small dog water fountain</t>
+          <t>metal dog fountain</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -6711,7 +6684,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6721,35 +6694,30 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>PETME2 | SP | Discovery | Auto</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>20261005</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>Auto</t>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>paused</t>
-        </is>
-      </c>
-      <c r="P142" t="n">
-        <v>5</v>
-      </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>Dynamic bids - down only</t>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S142" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>steel cat fountain</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6729,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6771,7 +6739,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -6779,14 +6752,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S143" t="n">
+        <v>0.8</v>
+      </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>replacement</t>
+          <t>stainless steel dog water fountain</t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6774,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6808,7 +6784,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -6816,14 +6797,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S144" t="n">
+        <v>0.83</v>
+      </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>stainless steel pet water fountain</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6819,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6845,7 +6829,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -6853,14 +6842,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S145" t="n">
+        <v>0.83</v>
+      </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>bird</t>
+          <t>stainless steel pet fountain</t>
         </is>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6864,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6882,7 +6874,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -6890,14 +6887,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S146" t="n">
+        <v>0.83</v>
+      </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>stainless steel cat fountain</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6919,7 +6919,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -6927,14 +6932,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S147" t="n">
+        <v>0.77</v>
+      </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>slow feeder</t>
+          <t>dog water fountain stainless steel</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6954,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6956,7 +6964,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -6964,14 +6977,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S148" t="n">
+        <v>0.83</v>
+      </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>petme2</t>
+          <t>pet water fountain stainless steel</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6999,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -6993,7 +7009,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -7001,14 +7022,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S149" t="n">
+        <v>0.83</v>
+      </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>gravity</t>
+          <t>stainless steel water fountain for cats</t>
         </is>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7044,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7030,17 +7054,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Auto-Feeders</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Auto - 3L Feeders + Camera</t>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -7048,8 +7067,18 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="R150" t="n">
-        <v>0.4</v>
+      <c r="S150" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>stainless steel water fountain for dogs</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -7060,7 +7089,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7070,12 +7099,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Auto-Feeders</t>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -7083,9 +7112,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>LW-EZAJ-KKZD</t>
+      <c r="S151" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>metal dog water fountain</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7134,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7107,12 +7144,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Auto-Feeders</t>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -7120,9 +7157,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>93-E8EG-20UY</t>
+      <c r="S152" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>metal pet water fountain</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7179,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7144,12 +7189,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Auto-Feeders</t>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -7157,9 +7202,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>2H-2T1T-CJC3</t>
+      <c r="S153" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>108oz cat water fountain</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7224,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7181,17 +7234,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Auto-WiFi</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>Auto - WiFi Feeder</t>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -7199,8 +7247,18 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="R154" t="n">
-        <v>0.2</v>
+      <c r="S154" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>3.2l cat water fountain</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -7211,7 +7269,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7221,12 +7279,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Auto-WiFi</t>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -7234,9 +7292,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>QO-7VBS-CVT4</t>
+      <c r="S155" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>108 oz pet water fountain</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7314,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7258,17 +7324,12 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Auto-Stainless</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>Auto - Stainless Fountain</t>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -7276,8 +7337,18 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="R156" t="n">
+      <c r="S156" t="n">
         <v>0.4</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>large cat water fountain stainless steel</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -7288,7 +7359,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7298,12 +7369,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Auto-Stainless</t>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -7311,9 +7382,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>QY-HHE8-0H1B</t>
+      <c r="S157" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>cat water fountain with led light</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7404,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7335,17 +7414,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Auto-Fountains</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Auto - $19.99 Fountains</t>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -7353,8 +7427,18 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="R158" t="n">
-        <v>0.22</v>
+      <c r="S158" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>pet water fountain with led light</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -7365,7 +7449,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7375,12 +7459,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Auto-Fountains</t>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -7388,9 +7472,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>L6-L3S1-I7Q6</t>
+      <c r="S159" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>faucet cat water fountain</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7494,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7412,12 +7504,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>PETME2-SP-Discovery</t>
+          <t>PETME2-SP-KeywordTest</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Auto-Fountains</t>
+          <t>Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -7425,9 +7517,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>SD-85ET-IOZ3</t>
+      <c r="S160" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>cat water fountain dishwasher safe</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -7439,30 +7539,3415 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S161" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>cat water fountain for multiple cats</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S162" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>quiet stainless steel cat water fountain</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S163" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>large capacity cat water fountain</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S164" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>dog water fountain for small dogs</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S165" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>water fountains for cats indoor</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>cat fountain stainless steel</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S167" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>cat fountains</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S168" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>water fountain for dogs</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S169" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>dog fountain stainless steel</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S170" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>cat stainless steel water fountain</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S171" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>dog drinking fountain</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S172" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>cat drinking fountain stainless steel</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S173" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>stainless cat water fountain</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S174" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>metal water fountain for cats</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S175" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>metal cat fountain</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S176" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>large capacity dog water fountain</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S177" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>large capacity pet water fountain</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S178" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>cat water fountain with led indicator</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S179" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>cat waterer</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S180" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>large pet water fountain</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S181" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>easy to clean cat water fountain</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S182" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>dishwasher safe cat water fountain</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Test-StainlessFountain</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S183" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>steel cat water fountain</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Ad Group</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Test - Basic Fountains</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="R184" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
           <t>Product Ad</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Create</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>L6-L3S1-I7Q6</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Product Ad</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>SD-85ET-IOZ3</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Product Ad</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>JE-LQEW-9EHL</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S189" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>cat fountain</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S190" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>pet fountain</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S191" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>cat water dispenser</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S192" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>cat drinking fountain</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S193" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>pet water dispenser</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S194" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>kitty water fountain</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S195" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>pet drinking fountain</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S196" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>quiet cat water fountain</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S197" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>cat water fountain quiet</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S198" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>silent cat water fountain</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S199" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>pet water fountain for cats</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S200" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>cat water fountain for indoor cats</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S201" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>water fountain for cats indoor</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S202" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>plastic cat water fountain</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S203" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>cat water fountain with water level window</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S204" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>pet water fountain for small dogs</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S205" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>kitten water fountain</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S206" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>water bowl fountain for cats</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S207" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>small dog water fountain</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S208" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>water dispenser for cats</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S209" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>kitty fountain</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S210" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>quiet pet water fountain</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S211" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>small pet water fountain</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S212" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>small water fountain for cats</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S213" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>kitten fountain</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>PETME2-SP-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Test-BasicFountains</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S214" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>water fountain for small dogs</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Campaign</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
         <is>
           <t>PETME2-SP-Discovery</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>PETME2 | SP | Discovery | Auto</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>paused</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>5</v>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Campaign Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>replacement</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Campaign Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>pump</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Campaign Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>bird</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Campaign Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Campaign Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>slow feeder</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Campaign Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>petme2</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Campaign Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>gravity</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Campaign Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Campaign Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>wireless</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Campaign Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>ceramic</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Campaign Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Campaign Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>heated</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Campaign Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>large dog</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Campaign Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>wet food</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Ad Group</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Auto-Feeders</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Auto - 3L Feeders + Camera</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="R230" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Product Ad</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Auto-Feeders</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>LW-EZAJ-KKZD</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Product Ad</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Auto-Feeders</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>93-E8EG-20UY</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Product Ad</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Auto-Feeders</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>2H-2T1T-CJC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Ad Group</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Auto-WiFi</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Auto - WiFi Feeder</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="R234" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Product Ad</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Auto-WiFi</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>QO-7VBS-CVT4</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Ad Group</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Auto-Stainless</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Auto - Stainless Fountain</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="R236" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Product Ad</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Auto-Stainless</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>QY-HHE8-0H1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Ad Group</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
         <is>
           <t>Auto-Fountains</t>
         </is>
       </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="Q161" t="inlineStr">
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Auto - $19.99 Fountains</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="R238" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Product Ad</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Auto-Fountains</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>L6-L3S1-I7Q6</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Product Ad</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Auto-Fountains</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>SD-85ET-IOZ3</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Product Ad</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>PETME2-SP-Discovery</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Auto-Fountains</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
         <is>
           <t>JE-LQEW-9EHL</t>
         </is>
